--- a/service_booking_forms/048_spa_appointment_form--service_booking_forms.xlsx
+++ b/service_booking_forms/048_spa_appointment_form--service_booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'staff_member_1',_'label':_'john_doe',_'value':_'staff_member_1'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'staff_member_1', 'label': 'John Doe', 'value': 'staff_member_1'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'staff_member_2',_'label':_'jane_doe',_'value':_'staff_member_2'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'staff_member_2', 'label': 'Jane Doe', 'value': 'staff_member_2'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'confirmed',_'label':_'confirmed',_'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'confirmed', 'label': 'Confirmed', 'value': 'confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'pending',_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'pending', 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'cancelled',_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'cancelled', 'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'no_show',_'label':_'no_show',_'value':_'no_show'}</t>
+          <t>no_show</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'no_show', 'label': 'No Show', 'value': 'no_show'}</t>
+          <t>No Show</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'credit_card',_'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'credit_card', 'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'cash',_'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'cash', 'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'bank_transfer',_'label':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'bank_transfer', 'label': 'Bank Transfer', 'value': 'bank_transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
